--- a/server/uploads/predictions/Ennustus.xlsx
+++ b/server/uploads/predictions/Ennustus.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\meie\ppa\users\38902015222\My Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\38902015222\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66B0951D-4F38-C547-8B9F-AA2F7E2F752C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DBE67AEC-E997-8B4B-B544-479FBEECB42B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19250" yWindow="-7710" windowWidth="28840" windowHeight="20880" xr2:uid="{71ACDA5A-2A4F-42DF-A035-BA793F8CA08E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{71ACDA5A-2A4F-42DF-A035-BA793F8CA08E}"/>
   </bookViews>
   <sheets>
     <sheet name="Ennustus" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="75">
   <si>
     <t>Kodus</t>
   </si>
@@ -71,12 +71,6 @@
     <t>MEX</t>
   </si>
   <si>
-    <t>LAV</t>
-  </si>
-  <si>
-    <t>Avo</t>
-  </si>
-  <si>
     <t>KOR</t>
   </si>
   <si>
@@ -95,15 +89,9 @@
     <t>QAT</t>
   </si>
   <si>
-    <t>SWI</t>
-  </si>
-  <si>
     <t>BRA</t>
   </si>
   <si>
-    <t>MOR</t>
-  </si>
-  <si>
     <t>HAI</t>
   </si>
   <si>
@@ -125,12 +113,6 @@
     <t>GER</t>
   </si>
   <si>
-    <t>CUR</t>
-  </si>
-  <si>
-    <t>CDI</t>
-  </si>
-  <si>
     <t>ECU</t>
   </si>
   <si>
@@ -155,21 +137,6 @@
     <t>IRN</t>
   </si>
   <si>
-    <t>NZE</t>
-  </si>
-  <si>
-    <t>SPA</t>
-  </si>
-  <si>
-    <t>CAP</t>
-  </si>
-  <si>
-    <t>SAU</t>
-  </si>
-  <si>
-    <t>URU</t>
-  </si>
-  <si>
     <t>FRA</t>
   </si>
   <si>
@@ -197,9 +164,6 @@
     <t>POR</t>
   </si>
   <si>
-    <t>CON</t>
-  </si>
-  <si>
     <t>UZB</t>
   </si>
   <si>
@@ -221,103 +185,79 @@
     <t>MatchID</t>
   </si>
   <si>
-    <t>Hispaania</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curacao </t>
-  </si>
-  <si>
-    <t>Holland</t>
-  </si>
-  <si>
-    <t>Iraan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iraak </t>
-  </si>
-  <si>
-    <t>Šveits</t>
-  </si>
-  <si>
-    <t>Paraguay</t>
-  </si>
-  <si>
-    <t>Ghana</t>
-  </si>
-  <si>
-    <t>Maroko</t>
-  </si>
-  <si>
-    <t>Saksamaa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gabo Verde </t>
-  </si>
-  <si>
-    <t>Belgia</t>
-  </si>
-  <si>
-    <t>Austraalia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Austria </t>
-  </si>
-  <si>
-    <t xml:space="preserve">congo </t>
-  </si>
-  <si>
-    <t>Tuneesia</t>
-  </si>
-  <si>
-    <t>Alžeeria</t>
-  </si>
-  <si>
-    <t>Norra</t>
-  </si>
-  <si>
-    <t>Rootsi</t>
-  </si>
-  <si>
-    <t>Jaapan</t>
-  </si>
-  <si>
-    <t>Türgi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kanada </t>
-  </si>
-  <si>
-    <t>Mehhiko</t>
-  </si>
-  <si>
-    <t>Ecuador</t>
-  </si>
-  <si>
-    <t>Šotimaa</t>
-  </si>
-  <si>
-    <t>Haiti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Korea </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tšehhi </t>
-  </si>
-  <si>
-    <t>Egiptus</t>
-  </si>
-  <si>
-    <t>Jordaania</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saudi Araabia </t>
-  </si>
-  <si>
-    <t>Prantsusmaa</t>
+    <t>CIV</t>
+  </si>
+  <si>
+    <t>CUW</t>
+  </si>
+  <si>
+    <t>RSA</t>
+  </si>
+  <si>
+    <t>SUI</t>
+  </si>
+  <si>
+    <t>MAR</t>
+  </si>
+  <si>
+    <t>NZL</t>
+  </si>
+  <si>
+    <t>URY</t>
+  </si>
+  <si>
+    <t>KSA</t>
+  </si>
+  <si>
+    <t>ESP</t>
+  </si>
+  <si>
+    <t>COD</t>
+  </si>
+  <si>
+    <t>CPV</t>
+  </si>
+  <si>
+    <t>PUNKTISÜSTEEM</t>
+  </si>
+  <si>
+    <t>Täpne skoor</t>
+  </si>
+  <si>
+    <t>3p</t>
+  </si>
+  <si>
+    <t>1p</t>
+  </si>
+  <si>
+    <t>Õige tulemus</t>
+  </si>
+  <si>
+    <t>Vale tulemus</t>
+  </si>
+  <si>
+    <t>0p</t>
+  </si>
+  <si>
+    <t>2p</t>
+  </si>
+  <si>
+    <t>4p</t>
+  </si>
+  <si>
+    <t>Finalist</t>
+  </si>
+  <si>
+    <t>5p</t>
+  </si>
+  <si>
+    <t>10p</t>
+  </si>
+  <si>
+    <t>Pronksi võitja</t>
+  </si>
+  <si>
+    <t>32 parimat iga õige riik</t>
   </si>
 </sst>
 </file>
@@ -819,8 +759,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% – rõhk1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -866,7 +810,101 @@
     <cellStyle name="Väljund" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Üldpealkiri" xfId="1" builtinId="15" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="31">
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -880,7 +918,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BF95AC62-11FD-49DB-990B-62DD2EE22065}" name="Tabel2" displayName="Tabel2" ref="A1:E73" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BF95AC62-11FD-49DB-990B-62DD2EE22065}" name="Tabel2" displayName="Tabel2" ref="A1:E73" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:E73" xr:uid="{BF95AC62-11FD-49DB-990B-62DD2EE22065}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -889,107 +927,107 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="5" xr3:uid="{85CB64AC-741A-4259-9986-DB920FE95B88}" name="MatchID"/>
-    <tableColumn id="1" xr3:uid="{34B04134-1607-45D0-A246-F117BCCEC5CC}" name="Kodus"/>
-    <tableColumn id="2" xr3:uid="{947A7D0A-C91F-4281-883E-B74656207801}" name="SkoorK"/>
-    <tableColumn id="3" xr3:uid="{320560EF-E025-4FD1-8151-FA4841C9C8C8}" name="SkoorV"/>
-    <tableColumn id="4" xr3:uid="{85DEFBC7-BBF9-4F8E-A0A6-6D798EF8A15B}" name="Võõrsil"/>
+    <tableColumn id="5" xr3:uid="{85CB64AC-741A-4259-9986-DB920FE95B88}" name="MatchID" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{34B04134-1607-45D0-A246-F117BCCEC5CC}" name="Kodus" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{947A7D0A-C91F-4281-883E-B74656207801}" name="SkoorK" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{320560EF-E025-4FD1-8151-FA4841C9C8C8}" name="SkoorV" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{85DEFBC7-BBF9-4F8E-A0A6-6D798EF8A15B}" name="Võõrsil" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{05451F19-3615-49BC-831A-2C772F8474A8}" name="Tabel3" displayName="Tabel3" ref="G1:G33" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{05451F19-3615-49BC-831A-2C772F8474A8}" name="Tabel3" displayName="Tabel3" ref="G1:G33" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
   <autoFilter ref="G1:G33" xr:uid="{05451F19-3615-49BC-831A-2C772F8474A8}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{2E32A73A-3FCC-4ED4-9CB1-B4AF50CAA9D6}" name="32 parimat"/>
+    <tableColumn id="1" xr3:uid="{2E32A73A-3FCC-4ED4-9CB1-B4AF50CAA9D6}" name="32 parimat" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D9F22127-C7E3-43D6-843F-EE707F468651}" name="Tabel1" displayName="Tabel1" ref="I1:I17" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D9F22127-C7E3-43D6-843F-EE707F468651}" name="Tabel1" displayName="Tabel1" ref="I1:I17" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <autoFilter ref="I1:I17" xr:uid="{D9F22127-C7E3-43D6-843F-EE707F468651}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{A120E8E2-A251-4092-B302-63B377FD88B9}" name="16 parimat"/>
+    <tableColumn id="1" xr3:uid="{A120E8E2-A251-4092-B302-63B377FD88B9}" name="16 parimat" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{22D15C93-473A-4886-B1CB-6C0C1792C739}" name="Tabel4" displayName="Tabel4" ref="K1:K9" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{22D15C93-473A-4886-B1CB-6C0C1792C739}" name="Tabel4" displayName="Tabel4" ref="K1:K9" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
   <autoFilter ref="K1:K9" xr:uid="{22D15C93-473A-4886-B1CB-6C0C1792C739}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{8D7BBBDC-9982-4CF8-8157-C6CDB90993A3}" name="8 parimat"/>
+    <tableColumn id="1" xr3:uid="{8D7BBBDC-9982-4CF8-8157-C6CDB90993A3}" name="8 parimat" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AB0D0EC6-BCA2-4342-BBD1-4AC334A2502E}" name="Tabel5" displayName="Tabel5" ref="M1:M5" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AB0D0EC6-BCA2-4342-BBD1-4AC334A2502E}" name="Tabel5" displayName="Tabel5" ref="M1:M5" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
   <autoFilter ref="M1:M5" xr:uid="{AB0D0EC6-BCA2-4342-BBD1-4AC334A2502E}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{3DAF31B1-104B-4D1C-A740-81B4DDA20252}" name="4 parimat"/>
+    <tableColumn id="1" xr3:uid="{3DAF31B1-104B-4D1C-A740-81B4DDA20252}" name="4 parimat" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DCFB02CF-5FC8-4E85-882C-1CD778AE0935}" name="Tabel6" displayName="Tabel6" ref="N1:N2" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DCFB02CF-5FC8-4E85-882C-1CD778AE0935}" name="Tabel6" displayName="Tabel6" ref="N1:N2" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <autoFilter ref="N1:N2" xr:uid="{DCFB02CF-5FC8-4E85-882C-1CD778AE0935}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{FCBCB793-577F-49F1-BC3A-988B7E3E3686}" name="3. koha võitja"/>
+    <tableColumn id="1" xr3:uid="{FCBCB793-577F-49F1-BC3A-988B7E3E3686}" name="3. koha võitja" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6DA759E2-96DE-4FE7-8B94-BC5199EEDAA0}" name="Tabel7" displayName="Tabel7" ref="O1:O3" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6DA759E2-96DE-4FE7-8B94-BC5199EEDAA0}" name="Tabel7" displayName="Tabel7" ref="O1:O3" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <autoFilter ref="O1:O3" xr:uid="{6DA759E2-96DE-4FE7-8B94-BC5199EEDAA0}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{F3B75B3B-ECC2-4833-81DC-34D7A299546F}" name="Finaal"/>
+    <tableColumn id="1" xr3:uid="{F3B75B3B-ECC2-4833-81DC-34D7A299546F}" name="Finaal" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{D863855E-992F-45CA-AFD2-8F65C4CDF7DC}" name="Tabel8" displayName="Tabel8" ref="Q1:Q2" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{D863855E-992F-45CA-AFD2-8F65C4CDF7DC}" name="Tabel8" displayName="Tabel8" ref="Q1:Q2" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
   <autoFilter ref="Q1:Q2" xr:uid="{D863855E-992F-45CA-AFD2-8F65C4CDF7DC}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{EA5AC2AE-CDA2-4A87-AE10-FF93946883F2}" name="Maailmameister"/>
+    <tableColumn id="1" xr3:uid="{EA5AC2AE-CDA2-4A87-AE10-FF93946883F2}" name="Maailmameister" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{4ACF8729-BADB-4292-934F-41376E9562F9}" name="Tabel10" displayName="Tabel10" ref="S1:S2" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{4ACF8729-BADB-4292-934F-41376E9562F9}" name="Tabel10" displayName="Tabel10" ref="S1:S2" totalsRowShown="0" headerRowDxfId="2" dataDxfId="1">
   <autoFilter ref="S1:S2" xr:uid="{4ACF8729-BADB-4292-934F-41376E9562F9}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{BA581C37-D284-497D-B3F8-1FA69DC3B4BC}" name="Ennustaja"/>
+    <tableColumn id="1" xr3:uid="{BA581C37-D284-497D-B3F8-1FA69DC3B4BC}" name="Ennustaja" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1315,12 +1353,13 @@
   <dimension ref="A1:S73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.76171875" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="8.47265625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="6.58984375" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="7.26171875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.22265625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.22265625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.28125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.38671875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.28125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.64453125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="6.3203125" bestFit="1" customWidth="1"/>
@@ -1330,7 +1369,7 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1357,7 +1396,7 @@
         <v>7</v>
       </c>
       <c r="N1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O1" t="s">
         <v>8</v>
@@ -1370,1203 +1409,1072 @@
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>537327</v>
+      </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
       <c r="E2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="S2" s="1"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>537328</v>
+      </c>
+      <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I2" t="s">
-        <v>64</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-      <c r="N2" t="s">
-        <v>88</v>
-      </c>
-      <c r="O2" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>94</v>
-      </c>
-      <c r="S2" t="s">
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s">
-        <v>63</v>
-      </c>
-      <c r="I3" t="s">
-        <v>71</v>
-      </c>
-      <c r="K3" t="s">
-        <v>64</v>
-      </c>
-      <c r="M3" t="s">
-        <v>64</v>
-      </c>
-      <c r="O3" t="s">
-        <v>71</v>
-      </c>
+      <c r="G3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>537329</v>
+      </c>
       <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
       <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" t="s">
-        <v>64</v>
-      </c>
-      <c r="I4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="M4" t="s">
-        <v>62</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="M4" s="1"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>537330</v>
+      </c>
       <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
       <c r="E5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" t="s">
-        <v>65</v>
-      </c>
-      <c r="I5" t="s">
-        <v>79</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>4</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>537331</v>
+      </c>
       <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
       <c r="E6" t="s">
         <v>11</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>537332</v>
+      </c>
+      <c r="B7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>537333</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>537334</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>537335</v>
+      </c>
+      <c r="B10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>537336</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>537337</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>537338</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="L13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M13" s="2"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>537339</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="L14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>537340</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="L15" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>537342</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="L16" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="I6" t="s">
-        <v>80</v>
-      </c>
-      <c r="K6">
+      <c r="M16" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>537341</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="L17" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>537343</v>
+      </c>
+      <c r="B18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="1"/>
+      <c r="L18" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" t="s">
-        <v>67</v>
-      </c>
-      <c r="I7" t="s">
-        <v>90</v>
-      </c>
-      <c r="K7">
+      <c r="M18" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>537344</v>
+      </c>
+      <c r="B19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="L19" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" t="s">
-        <v>68</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="M19" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>537345</v>
+      </c>
+      <c r="B20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="1"/>
+      <c r="L20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>537346</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" s="1"/>
+      <c r="L21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>537348</v>
+      </c>
+      <c r="B22" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" s="1"/>
+      <c r="L22" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="K8" t="s">
+      <c r="M22" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10">
-        <v>2</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" t="s">
-        <v>70</v>
-      </c>
-      <c r="I10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11" t="s">
-        <v>19</v>
-      </c>
-      <c r="G11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12" t="s">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>537347</v>
+      </c>
+      <c r="B23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" s="1"/>
+      <c r="L23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M23" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="I12">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13">
-        <v>3</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13" t="s">
-        <v>19</v>
-      </c>
-      <c r="G13" t="s">
-        <v>73</v>
-      </c>
-      <c r="I13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B14" t="s">
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>537350</v>
+      </c>
+      <c r="B24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" s="1"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>537349</v>
+      </c>
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" t="s">
         <v>21</v>
       </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" t="s">
-        <v>74</v>
-      </c>
-      <c r="I14">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15" t="s">
-        <v>24</v>
-      </c>
-      <c r="G15" t="s">
-        <v>75</v>
-      </c>
-      <c r="I15">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" t="s">
-        <v>76</v>
-      </c>
-      <c r="I16">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" t="s">
-        <v>77</v>
-      </c>
-      <c r="I17">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18" t="s">
-        <v>21</v>
-      </c>
-      <c r="G18" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B20" t="s">
+      <c r="G25" s="1"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>537351</v>
+      </c>
+      <c r="B26" t="s">
         <v>25</v>
       </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" t="s">
+        <v>51</v>
+      </c>
+      <c r="G26" s="1"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>537352</v>
+      </c>
+      <c r="B27" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" t="s">
         <v>26</v>
       </c>
-      <c r="G20" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B21" t="s">
+      <c r="G27" s="1"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>537353</v>
+      </c>
+      <c r="B28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" t="s">
+        <v>50</v>
+      </c>
+      <c r="G28" s="1"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>537354</v>
+      </c>
+      <c r="B29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" t="s">
+        <v>51</v>
+      </c>
+      <c r="G29" s="1"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>537355</v>
+      </c>
+      <c r="B30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" t="s">
+        <v>25</v>
+      </c>
+      <c r="G30" s="1"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>537356</v>
+      </c>
+      <c r="B31" t="s">
+        <v>51</v>
+      </c>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" t="s">
+        <v>50</v>
+      </c>
+      <c r="G31" s="1"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>537357</v>
+      </c>
+      <c r="B32" t="s">
         <v>27</v>
       </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" t="s">
         <v>28</v>
       </c>
-      <c r="G21" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B22" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="G32" s="1"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>537358</v>
+      </c>
+      <c r="B33" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" t="s">
+        <v>30</v>
+      </c>
+      <c r="G33" s="1"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>537359</v>
+      </c>
+      <c r="B34" t="s">
         <v>27</v>
       </c>
-      <c r="G22" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B23" t="s">
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>537360</v>
+      </c>
+      <c r="B35" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" t="s">
         <v>28</v>
       </c>
-      <c r="C23">
-        <v>2</v>
-      </c>
-      <c r="D23">
-        <v>2</v>
-      </c>
-      <c r="E23" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B24" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24">
-        <v>2</v>
-      </c>
-      <c r="D24">
-        <v>2</v>
-      </c>
-      <c r="E24" t="s">
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>537361</v>
+      </c>
+      <c r="B36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" t="s">
         <v>27</v>
       </c>
-      <c r="G24" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" t="s">
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>537362</v>
+      </c>
+      <c r="B37" t="s">
         <v>28</v>
       </c>
-      <c r="C25">
-        <v>2</v>
-      </c>
-      <c r="D25">
-        <v>2</v>
-      </c>
-      <c r="E25" t="s">
-        <v>25</v>
-      </c>
-      <c r="G25" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B26" t="s">
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" t="s">
         <v>29</v>
       </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26">
-        <v>1</v>
-      </c>
-      <c r="E26" t="s">
-        <v>30</v>
-      </c>
-      <c r="G26" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B27" t="s">
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>537363</v>
+      </c>
+      <c r="B38" t="s">
         <v>31</v>
       </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" t="s">
         <v>32</v>
       </c>
-      <c r="G27" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
-      <c r="E28" t="s">
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>537364</v>
+      </c>
+      <c r="B39" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>537365</v>
+      </c>
+      <c r="B40" t="s">
         <v>31</v>
       </c>
-      <c r="G28" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B29" t="s">
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>537366</v>
+      </c>
+      <c r="B41" t="s">
+        <v>55</v>
+      </c>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" t="s">
         <v>32</v>
       </c>
-      <c r="C29">
-        <v>0</v>
-      </c>
-      <c r="D29">
-        <v>1</v>
-      </c>
-      <c r="E29" t="s">
-        <v>30</v>
-      </c>
-      <c r="G29" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B30" t="s">
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>537368</v>
+      </c>
+      <c r="B42" t="s">
         <v>32</v>
       </c>
-      <c r="C30">
-        <v>0</v>
-      </c>
-      <c r="D30">
-        <v>2</v>
-      </c>
-      <c r="E30" t="s">
-        <v>29</v>
-      </c>
-      <c r="G30" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B31" t="s">
-        <v>30</v>
-      </c>
-      <c r="C31">
-        <v>0</v>
-      </c>
-      <c r="D31">
-        <v>3</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>537367</v>
+      </c>
+      <c r="B43" t="s">
+        <v>55</v>
+      </c>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" t="s">
         <v>31</v>
       </c>
-      <c r="G31" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B32" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32">
-        <v>0</v>
-      </c>
-      <c r="D32">
-        <v>2</v>
-      </c>
-      <c r="E32" t="s">
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>537369</v>
+      </c>
+      <c r="B44" t="s">
+        <v>58</v>
+      </c>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>537370</v>
+      </c>
+      <c r="B45" t="s">
+        <v>57</v>
+      </c>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>537371</v>
+      </c>
+      <c r="B46" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>537372</v>
+      </c>
+      <c r="B47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>537373</v>
+      </c>
+      <c r="B48" t="s">
+        <v>56</v>
+      </c>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>537374</v>
+      </c>
+      <c r="B49" t="s">
+        <v>60</v>
+      </c>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>537391</v>
+      </c>
+      <c r="B50" t="s">
         <v>34</v>
       </c>
-      <c r="G32" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B33" t="s">
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" t="s">
         <v>35</v>
       </c>
-      <c r="C33">
-        <v>0</v>
-      </c>
-      <c r="D33">
-        <v>1</v>
-      </c>
-      <c r="E33" t="s">
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>537392</v>
+      </c>
+      <c r="B51" t="s">
         <v>36</v>
       </c>
-      <c r="G33" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B34" t="s">
-        <v>33</v>
-      </c>
-      <c r="C34">
-        <v>0</v>
-      </c>
-      <c r="D34">
-        <v>2</v>
-      </c>
-      <c r="E34" t="s">
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>537393</v>
+      </c>
+      <c r="B52" t="s">
+        <v>34</v>
+      </c>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>537394</v>
+      </c>
+      <c r="B53" t="s">
+        <v>37</v>
+      </c>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B35" t="s">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>537395</v>
+      </c>
+      <c r="B54" t="s">
+        <v>37</v>
+      </c>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>537396</v>
+      </c>
+      <c r="B55" t="s">
+        <v>35</v>
+      </c>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" t="s">
         <v>36</v>
       </c>
-      <c r="C35">
-        <v>2</v>
-      </c>
-      <c r="D35">
-        <v>1</v>
-      </c>
-      <c r="E35" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B36" t="s">
-        <v>36</v>
-      </c>
-      <c r="C36">
-        <v>2</v>
-      </c>
-      <c r="D36">
-        <v>0</v>
-      </c>
-      <c r="E36" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B37" t="s">
-        <v>34</v>
-      </c>
-      <c r="C37">
-        <v>2</v>
-      </c>
-      <c r="D37">
-        <v>2</v>
-      </c>
-      <c r="E37" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B38" t="s">
-        <v>37</v>
-      </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-      <c r="D38">
-        <v>1</v>
-      </c>
-      <c r="E38" t="s">
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>537397</v>
+      </c>
+      <c r="B56" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B39" t="s">
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" t="s">
         <v>39</v>
       </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-      <c r="D39">
-        <v>0</v>
-      </c>
-      <c r="E39" t="s">
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>537398</v>
+      </c>
+      <c r="B57" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B40" t="s">
-        <v>37</v>
-      </c>
-      <c r="C40">
-        <v>0</v>
-      </c>
-      <c r="D40">
-        <v>2</v>
-      </c>
-      <c r="E40" t="s">
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>537399</v>
+      </c>
+      <c r="B58" t="s">
+        <v>38</v>
+      </c>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>537400</v>
+      </c>
+      <c r="B59" t="s">
+        <v>41</v>
+      </c>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B41" t="s">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>537401</v>
+      </c>
+      <c r="B60" t="s">
+        <v>41</v>
+      </c>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>537402</v>
+      </c>
+      <c r="B61" t="s">
+        <v>39</v>
+      </c>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" t="s">
         <v>40</v>
       </c>
-      <c r="C41">
-        <v>0</v>
-      </c>
-      <c r="D41">
-        <v>1</v>
-      </c>
-      <c r="E41" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B42" t="s">
-        <v>38</v>
-      </c>
-      <c r="C42">
-        <v>2</v>
-      </c>
-      <c r="D42">
-        <v>1</v>
-      </c>
-      <c r="E42" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B43" t="s">
-        <v>40</v>
-      </c>
-      <c r="C43">
-        <v>2</v>
-      </c>
-      <c r="D43">
-        <v>0</v>
-      </c>
-      <c r="E43" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B44" t="s">
-        <v>41</v>
-      </c>
-      <c r="C44">
-        <v>2</v>
-      </c>
-      <c r="D44">
-        <v>0</v>
-      </c>
-      <c r="E44" t="s">
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>537403</v>
+      </c>
+      <c r="B62" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B45" t="s">
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>537404</v>
+      </c>
+      <c r="B63" t="s">
         <v>43</v>
       </c>
-      <c r="C45">
-        <v>5</v>
-      </c>
-      <c r="D45">
-        <v>2</v>
-      </c>
-      <c r="E45" t="s">
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B46" t="s">
-        <v>41</v>
-      </c>
-      <c r="C46">
-        <v>1</v>
-      </c>
-      <c r="D46">
-        <v>2</v>
-      </c>
-      <c r="E46" t="s">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>537405</v>
+      </c>
+      <c r="B64" t="s">
+        <v>42</v>
+      </c>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B47" t="s">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>537406</v>
+      </c>
+      <c r="B65" t="s">
         <v>44</v>
       </c>
-      <c r="C47">
-        <v>0</v>
-      </c>
-      <c r="D47">
-        <v>1</v>
-      </c>
-      <c r="E47" t="s">
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>537407</v>
+      </c>
+      <c r="B66" t="s">
+        <v>44</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B48" t="s">
-        <v>44</v>
-      </c>
-      <c r="C48">
-        <v>2</v>
-      </c>
-      <c r="D48">
-        <v>1</v>
-      </c>
-      <c r="E48" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B49" t="s">
-        <v>42</v>
-      </c>
-      <c r="C49">
-        <v>0</v>
-      </c>
-      <c r="D49">
-        <v>2</v>
-      </c>
-      <c r="E49" t="s">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>537408</v>
+      </c>
+      <c r="B67" t="s">
+        <v>59</v>
+      </c>
+      <c r="C67" s="1"/>
+      <c r="D67" s="1"/>
+      <c r="E67" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B50" t="s">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>537409</v>
+      </c>
+      <c r="B68" t="s">
         <v>45</v>
       </c>
-      <c r="C50">
-        <v>2</v>
-      </c>
-      <c r="D50">
-        <v>0</v>
-      </c>
-      <c r="E50" t="s">
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B51" t="s">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>537410</v>
+      </c>
+      <c r="B69" t="s">
         <v>47</v>
       </c>
-      <c r="C51">
-        <v>0</v>
-      </c>
-      <c r="D51">
-        <v>0</v>
-      </c>
-      <c r="E51" t="s">
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+      <c r="E69" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B52" t="s">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>537411</v>
+      </c>
+      <c r="B70" t="s">
         <v>45</v>
       </c>
-      <c r="C52">
-        <v>2</v>
-      </c>
-      <c r="D52">
-        <v>0</v>
-      </c>
-      <c r="E52" t="s">
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B53" t="s">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>537412</v>
+      </c>
+      <c r="B71" t="s">
         <v>48</v>
       </c>
-      <c r="D53">
-        <v>2</v>
-      </c>
-      <c r="E53" t="s">
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+      <c r="E71" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B54" t="s">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <v>537413</v>
+      </c>
+      <c r="B72" t="s">
         <v>48</v>
       </c>
-      <c r="C54">
-        <v>1</v>
-      </c>
-      <c r="D54">
-        <v>1</v>
-      </c>
-      <c r="E54" t="s">
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B55" t="s">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <v>537414</v>
+      </c>
+      <c r="B73" t="s">
         <v>46</v>
       </c>
-      <c r="C55">
-        <v>3</v>
-      </c>
-      <c r="D55">
-        <v>1</v>
-      </c>
-      <c r="E55" t="s">
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B56" t="s">
-        <v>49</v>
-      </c>
-      <c r="C56">
-        <v>2</v>
-      </c>
-      <c r="D56">
-        <v>0</v>
-      </c>
-      <c r="E56" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B57" t="s">
-        <v>51</v>
-      </c>
-      <c r="C57">
-        <v>1</v>
-      </c>
-      <c r="D57">
-        <v>2</v>
-      </c>
-      <c r="E57" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B58" t="s">
-        <v>49</v>
-      </c>
-      <c r="C58">
-        <v>0</v>
-      </c>
-      <c r="D58">
-        <v>2</v>
-      </c>
-      <c r="E58" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B59" t="s">
-        <v>52</v>
-      </c>
-      <c r="C59">
-        <v>0</v>
-      </c>
-      <c r="D59">
-        <v>1</v>
-      </c>
-      <c r="E59" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B60" t="s">
-        <v>52</v>
-      </c>
-      <c r="C60">
-        <v>2</v>
-      </c>
-      <c r="D60">
-        <v>1</v>
-      </c>
-      <c r="E60" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B61" t="s">
-        <v>50</v>
-      </c>
-      <c r="C61">
-        <v>0</v>
-      </c>
-      <c r="D61">
-        <v>0</v>
-      </c>
-      <c r="E61" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B62" t="s">
-        <v>53</v>
-      </c>
-      <c r="C62">
-        <v>0</v>
-      </c>
-      <c r="D62">
-        <v>2</v>
-      </c>
-      <c r="E62" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B63" t="s">
-        <v>55</v>
-      </c>
-      <c r="C63">
-        <v>0</v>
-      </c>
-      <c r="D63">
-        <v>0</v>
-      </c>
-      <c r="E63" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B64" t="s">
-        <v>53</v>
-      </c>
-      <c r="C64">
-        <v>0</v>
-      </c>
-      <c r="D64">
-        <v>1</v>
-      </c>
-      <c r="E64" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B65" t="s">
-        <v>56</v>
-      </c>
-      <c r="C65">
-        <v>0</v>
-      </c>
-      <c r="E65" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B66" t="s">
-        <v>56</v>
-      </c>
-      <c r="C66">
-        <v>0</v>
-      </c>
-      <c r="D66">
-        <v>0</v>
-      </c>
-      <c r="E66" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B67" t="s">
-        <v>54</v>
-      </c>
-      <c r="C67">
-        <v>2</v>
-      </c>
-      <c r="D67">
-        <v>0</v>
-      </c>
-      <c r="E67" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B68" t="s">
-        <v>57</v>
-      </c>
-      <c r="C68">
-        <v>2</v>
-      </c>
-      <c r="D68">
-        <v>0</v>
-      </c>
-      <c r="E68" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B69" t="s">
-        <v>59</v>
-      </c>
-      <c r="C69">
-        <v>0</v>
-      </c>
-      <c r="D69">
-        <v>1</v>
-      </c>
-      <c r="E69" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B70" t="s">
-        <v>57</v>
-      </c>
-      <c r="C70">
-        <v>1</v>
-      </c>
-      <c r="D70">
-        <v>2</v>
-      </c>
-      <c r="E70" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B71" t="s">
-        <v>60</v>
-      </c>
-      <c r="C71">
-        <v>1</v>
-      </c>
-      <c r="D71">
-        <v>1</v>
-      </c>
-      <c r="E71" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B72" t="s">
-        <v>60</v>
-      </c>
-      <c r="C72">
-        <v>1</v>
-      </c>
-      <c r="D72">
-        <v>0</v>
-      </c>
-      <c r="E72" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B73" t="s">
-        <v>58</v>
-      </c>
-      <c r="C73">
-        <v>1</v>
-      </c>
-      <c r="D73">
-        <v>1</v>
-      </c>
-      <c r="E73" t="s">
-        <v>59</v>
-      </c>
-    </row>
   </sheetData>
+  <sheetProtection sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="9">
     <tablePart r:id="rId1"/>
